--- a/classification_output/23453618-sq26-classification.xlsx
+++ b/classification_output/23453618-sq26-classification.xlsx
@@ -479,7 +479,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
@@ -503,7 +507,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
@@ -527,7 +535,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
@@ -551,7 +563,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>5</v>
       </c>
@@ -575,7 +591,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
@@ -623,7 +643,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
@@ -695,7 +719,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
@@ -719,7 +747,11 @@
           <t>C29</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
@@ -743,7 +775,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F13" t="n">
         <v>5</v>
       </c>
@@ -767,7 +803,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
@@ -815,7 +855,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
@@ -839,7 +883,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F17" t="n">
         <v>9</v>
       </c>
@@ -863,7 +911,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
@@ -887,7 +939,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F19" t="n">
         <v>18</v>
       </c>
@@ -911,7 +967,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
@@ -935,7 +995,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
@@ -959,7 +1023,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F22" t="n">
         <v>2</v>
       </c>
@@ -983,7 +1051,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
@@ -1007,7 +1079,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
@@ -1031,7 +1107,11 @@
           <t>C29</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F25" t="n">
         <v>2</v>
       </c>
@@ -1055,7 +1135,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
@@ -1103,7 +1187,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
@@ -1127,7 +1215,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F29" t="n">
         <v>4</v>
       </c>
@@ -1175,7 +1267,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F31" t="n">
         <v>2</v>
       </c>
@@ -1199,7 +1295,11 @@
           <t>C29</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
       <c r="F32" t="n">
         <v>20</v>
       </c>
@@ -1223,7 +1323,11 @@
           <t>C21</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F33" t="n">
         <v>7</v>
       </c>
@@ -1247,7 +1351,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F34" t="n">
         <v>2</v>
       </c>
@@ -1271,7 +1379,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F35" t="n">
         <v>8</v>
       </c>
@@ -1319,7 +1431,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F37" t="n">
         <v>14</v>
       </c>
@@ -1367,7 +1483,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F39" t="n">
         <v>4</v>
       </c>
@@ -1415,7 +1535,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
@@ -1439,7 +1563,11 @@
           <t>K63</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F42" t="n">
         <v>20</v>
       </c>
@@ -1463,7 +1591,11 @@
           <t>C18</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F43" t="n">
         <v>12</v>
       </c>
@@ -1487,7 +1619,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F44" t="n">
         <v>5</v>
       </c>
@@ -1511,7 +1647,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
@@ -1535,7 +1675,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>C22</t>
+        </is>
+      </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
@@ -1559,7 +1703,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
@@ -1583,7 +1731,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
       <c r="F48" t="n">
         <v>2</v>
       </c>
@@ -1607,7 +1759,11 @@
           <t>C29</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F49" t="n">
         <v>2</v>
       </c>
@@ -1631,7 +1787,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F50" t="n">
         <v>2</v>
       </c>
@@ -1655,7 +1815,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>N71</t>
+        </is>
+      </c>
       <c r="F51" t="n">
         <v>5</v>
       </c>
@@ -1679,7 +1843,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
       <c r="F52" t="n">
         <v>2</v>
       </c>
@@ -1727,7 +1895,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F54" t="n">
         <v>3</v>
       </c>
@@ -1823,7 +1995,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
       <c r="F58" t="n">
         <v>2</v>
       </c>
@@ -1847,7 +2023,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F59" t="n">
         <v>20</v>
       </c>
@@ -1871,7 +2051,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F60" t="n">
         <v>2</v>
       </c>
@@ -1895,7 +2079,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F61" t="n">
         <v>3</v>
       </c>
@@ -1919,7 +2107,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F62" t="n">
         <v>4</v>
       </c>
@@ -1943,7 +2135,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F63" t="n">
         <v>3</v>
       </c>
@@ -1967,7 +2163,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
@@ -1991,7 +2191,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F65" t="n">
         <v>2</v>
       </c>
@@ -2015,7 +2219,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
@@ -2039,7 +2247,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
@@ -2063,7 +2275,11 @@
           <t>C29</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F68" t="n">
         <v>2</v>
       </c>
@@ -2087,7 +2303,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F69" t="n">
         <v>2</v>
       </c>
@@ -2111,7 +2331,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
       <c r="F70" t="n">
         <v>4</v>
       </c>
@@ -2135,7 +2359,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F71" t="n">
         <v>2</v>
       </c>
@@ -2159,7 +2387,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F72" t="n">
         <v>2</v>
       </c>
@@ -2183,7 +2415,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F73" t="n">
         <v>2</v>
       </c>
@@ -2207,7 +2443,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F74" t="n">
         <v>20</v>
       </c>
@@ -2231,7 +2471,11 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F75" t="n">
         <v>14</v>
       </c>
@@ -2255,7 +2499,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
@@ -2279,7 +2527,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F77" t="n">
         <v>2</v>
       </c>
@@ -2303,7 +2555,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F78" t="n">
         <v>2</v>
       </c>
@@ -2327,7 +2583,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
@@ -2351,7 +2611,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F80" t="n">
         <v>20</v>
       </c>
@@ -2375,7 +2639,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F81" t="n">
         <v>4</v>
       </c>
@@ -2399,7 +2667,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
       <c r="F82" t="n">
         <v>20</v>
       </c>
@@ -2423,7 +2695,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
       <c r="F83" t="n">
         <v>2</v>
       </c>
@@ -2447,7 +2723,11 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F84" t="n">
         <v>5</v>
       </c>
@@ -2471,7 +2751,11 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F85" t="n">
         <v>2</v>
       </c>
@@ -2495,7 +2779,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
       <c r="F86" t="n">
         <v>17</v>
       </c>
@@ -2519,7 +2807,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F87" t="n">
         <v>4</v>
       </c>
@@ -2543,7 +2835,11 @@
           <t>E36</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F88" t="n">
         <v>16</v>
       </c>
@@ -2567,7 +2863,11 @@
           <t>C24</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F89" t="n">
         <v>5</v>
       </c>
@@ -2591,7 +2891,11 @@
           <t>C16</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F90" t="n">
         <v>2</v>
       </c>
@@ -2615,7 +2919,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
       <c r="F91" t="n">
         <v>7</v>
       </c>
@@ -2639,7 +2947,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F92" t="n">
         <v>20</v>
       </c>
@@ -2663,7 +2975,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>C30</t>
+        </is>
+      </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
@@ -2687,7 +3003,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F94" t="n">
         <v>11</v>
       </c>
@@ -2711,7 +3031,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
@@ -2735,7 +3059,11 @@
           <t>C24</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F96" t="n">
         <v>7</v>
       </c>
@@ -2759,7 +3087,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F97" t="n">
         <v>3</v>
       </c>
@@ -2780,10 +3112,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>E36</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F98" t="n">
         <v>3</v>
       </c>
@@ -2807,7 +3143,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F99" t="n">
         <v>2</v>
       </c>
@@ -2828,10 +3168,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>E36</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>K62</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
         <v>17</v>
       </c>
@@ -2855,7 +3199,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F101" t="n">
         <v>4</v>
       </c>
@@ -2879,7 +3227,11 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F102" t="n">
         <v>16</v>
       </c>
@@ -2927,7 +3279,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F104" t="n">
         <v>5</v>
       </c>
@@ -2951,7 +3307,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
@@ -2975,7 +3335,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
       <c r="F106" t="n">
         <v>4</v>
       </c>
@@ -2999,7 +3363,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
       <c r="F107" t="n">
         <v>3</v>
       </c>
@@ -3023,7 +3391,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
       <c r="F108" t="n">
         <v>12</v>
       </c>
@@ -3047,7 +3419,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
       <c r="F109" t="n">
         <v>1</v>
       </c>
@@ -3071,7 +3447,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>N69</t>
+        </is>
+      </c>
       <c r="F110" t="n">
         <v>5</v>
       </c>
@@ -3095,7 +3475,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F111" t="n">
         <v>2</v>
       </c>
@@ -3119,7 +3503,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
       <c r="F112" t="n">
         <v>2</v>
       </c>
@@ -3143,7 +3531,11 @@
           <t>C24</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F113" t="n">
         <v>1</v>
       </c>
@@ -3167,7 +3559,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F114" t="n">
         <v>5</v>
       </c>
@@ -3191,7 +3587,11 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F115" t="n">
         <v>6</v>
       </c>
@@ -3215,7 +3615,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
       <c r="F116" t="n">
         <v>9</v>
       </c>
@@ -3239,7 +3643,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>N69</t>
+        </is>
+      </c>
       <c r="F117" t="n">
         <v>2</v>
       </c>
@@ -3263,7 +3671,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>J58</t>
+        </is>
+      </c>
       <c r="F118" t="n">
         <v>2</v>
       </c>
@@ -3287,7 +3699,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F119" t="n">
         <v>2</v>
       </c>
@@ -3311,7 +3727,11 @@
           <t>C22</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
       <c r="F120" t="n">
         <v>6</v>
       </c>
@@ -3335,7 +3755,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
@@ -3359,7 +3783,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
       <c r="F122" t="n">
         <v>2</v>
       </c>
@@ -3383,7 +3811,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
       <c r="F123" t="n">
         <v>6</v>
       </c>
@@ -3407,7 +3839,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
       <c r="F124" t="n">
         <v>18</v>
       </c>
@@ -3431,7 +3867,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>J58</t>
+        </is>
+      </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
@@ -3455,7 +3895,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F126" t="n">
         <v>2</v>
       </c>
@@ -3479,7 +3923,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F127" t="n">
         <v>2</v>
       </c>
@@ -3503,7 +3951,11 @@
           <t>C29</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F128" t="n">
         <v>4</v>
       </c>
@@ -3527,7 +3979,11 @@
           <t>C24</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F129" t="n">
         <v>10</v>
       </c>
@@ -3551,7 +4007,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F130" t="n">
         <v>6</v>
       </c>
@@ -3575,7 +4035,11 @@
           <t>C10</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
       <c r="F131" t="n">
         <v>17</v>
       </c>
@@ -3599,7 +4063,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
       <c r="F132" t="n">
         <v>2</v>
       </c>
@@ -3623,7 +4091,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
       <c r="F133" t="n">
         <v>2</v>
       </c>
@@ -3647,7 +4119,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F134" t="n">
         <v>7</v>
       </c>
@@ -3671,7 +4147,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F135" t="n">
         <v>2</v>
       </c>
@@ -3692,10 +4172,14 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
         <v>2</v>
       </c>
@@ -3719,7 +4203,11 @@
           <t>E36</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F137" t="n">
         <v>3</v>
       </c>
@@ -3743,7 +4231,11 @@
           <t>C10</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F138" t="n">
         <v>2</v>
       </c>
@@ -3767,7 +4259,11 @@
           <t>C20</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F139" t="n">
         <v>7</v>
       </c>
@@ -3791,7 +4287,11 @@
           <t>C21</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F140" t="n">
         <v>7</v>
       </c>
@@ -3815,7 +4315,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
       <c r="F141" t="n">
         <v>6</v>
       </c>
@@ -3839,7 +4343,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F142" t="n">
         <v>2</v>
       </c>
@@ -3863,7 +4371,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F143" t="n">
         <v>2</v>
       </c>
@@ -3887,7 +4399,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F144" t="n">
         <v>7</v>
       </c>
@@ -3911,7 +4427,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F145" t="n">
         <v>12</v>
       </c>
@@ -3959,7 +4479,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F147" t="n">
         <v>5</v>
       </c>
@@ -3983,7 +4507,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F148" t="n">
         <v>3</v>
       </c>
@@ -4007,7 +4535,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
       <c r="F149" t="n">
         <v>6</v>
       </c>
@@ -4031,7 +4563,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F150" t="n">
         <v>2</v>
       </c>
@@ -4055,7 +4591,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F151" t="n">
         <v>1</v>
       </c>
@@ -4079,7 +4619,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F152" t="n">
         <v>1</v>
       </c>
@@ -4103,7 +4647,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F153" t="n">
         <v>1</v>
       </c>
@@ -4127,7 +4675,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F154" t="n">
         <v>1</v>
       </c>
@@ -4175,7 +4727,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F156" t="n">
         <v>1</v>
       </c>
@@ -4199,7 +4755,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
       <c r="F157" t="n">
         <v>2</v>
       </c>
@@ -4271,7 +4831,11 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F160" t="n">
         <v>2</v>
       </c>
@@ -4295,7 +4859,11 @@
           <t>J59</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F161" t="n">
         <v>2</v>
       </c>
@@ -4319,7 +4887,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F162" t="n">
         <v>2</v>
       </c>
@@ -4343,7 +4915,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
@@ -4367,7 +4943,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
       <c r="F164" t="n">
         <v>2</v>
       </c>
@@ -4391,7 +4971,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>B08</t>
+        </is>
+      </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
@@ -4415,7 +4999,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
       <c r="F166" t="n">
         <v>2</v>
       </c>
@@ -4439,7 +5027,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F167" t="n">
         <v>2</v>
       </c>
@@ -4463,7 +5055,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F168" t="n">
         <v>4</v>
       </c>
@@ -4487,7 +5083,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
       <c r="F169" t="n">
         <v>12</v>
       </c>
@@ -4511,7 +5111,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>1</v>
       </c>
@@ -4535,7 +5139,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
       <c r="F171" t="n">
         <v>2</v>
       </c>
@@ -4607,7 +5215,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
       <c r="F174" t="n">
         <v>2</v>
       </c>
@@ -4631,7 +5243,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>1</v>
       </c>
@@ -4655,7 +5271,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F176" t="n">
         <v>4</v>
       </c>
@@ -4679,7 +5299,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>15</v>
       </c>
@@ -4703,7 +5327,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>1</v>
       </c>
@@ -4727,7 +5355,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>2</v>
       </c>
@@ -4751,7 +5383,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>2</v>
       </c>
@@ -4799,7 +5435,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>12</v>
       </c>
@@ -4823,7 +5463,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F183" t="n">
         <v>1</v>
       </c>
@@ -4847,7 +5491,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F184" t="n">
         <v>5</v>
       </c>
@@ -4871,7 +5519,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F185" t="n">
         <v>2</v>
       </c>
@@ -4895,7 +5547,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>2</v>
       </c>
@@ -4919,7 +5575,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F187" t="n">
         <v>4</v>
       </c>
@@ -4943,7 +5603,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F188" t="n">
         <v>4</v>
       </c>
@@ -4967,7 +5631,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F189" t="n">
         <v>2</v>
       </c>
@@ -4991,7 +5659,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F190" t="n">
         <v>20</v>
       </c>
@@ -5015,7 +5687,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F191" t="n">
         <v>1</v>
       </c>
@@ -5039,7 +5715,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F192" t="n">
         <v>6</v>
       </c>
@@ -5063,7 +5743,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
       <c r="F193" t="n">
         <v>2</v>
       </c>
@@ -5087,7 +5771,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F194" t="n">
         <v>7</v>
       </c>
@@ -5111,7 +5799,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F195" t="n">
         <v>2</v>
       </c>
@@ -5156,10 +5848,14 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F197" t="n">
         <v>6</v>
       </c>
@@ -5183,7 +5879,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F198" t="n">
         <v>6</v>
       </c>
@@ -5207,7 +5907,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
       <c r="F199" t="n">
         <v>3</v>
       </c>
@@ -5231,7 +5935,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F200" t="n">
         <v>3</v>
       </c>
@@ -5255,7 +5963,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F201" t="n">
         <v>2</v>
       </c>
@@ -5279,7 +5991,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F202" t="n">
         <v>2</v>
       </c>
@@ -5303,7 +6019,11 @@
           <t>C23</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F203" t="n">
         <v>9</v>
       </c>
@@ -5327,7 +6047,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F204" t="n">
         <v>6</v>
       </c>
@@ -5351,7 +6075,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
       <c r="F205" t="n">
         <v>2</v>
       </c>
@@ -5375,7 +6103,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F206" t="n">
         <v>1</v>
       </c>
@@ -5423,7 +6155,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F208" t="n">
         <v>1</v>
       </c>
@@ -5447,7 +6183,11 @@
           <t>C10</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
       <c r="F209" t="n">
         <v>1</v>
       </c>
@@ -5495,7 +6235,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F211" t="n">
         <v>2</v>
       </c>
@@ -5519,7 +6263,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
       <c r="F212" t="n">
         <v>2</v>
       </c>
@@ -5591,7 +6339,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
       <c r="F215" t="n">
         <v>1</v>
       </c>
@@ -5615,7 +6367,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F216" t="n">
         <v>5</v>
       </c>
@@ -5663,7 +6419,11 @@
           <t>L64</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F218" t="n">
         <v>3</v>
       </c>
@@ -5687,7 +6447,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
       <c r="F219" t="n">
         <v>16</v>
       </c>
@@ -5711,7 +6475,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F220" t="n">
         <v>20</v>
       </c>
@@ -5735,7 +6503,11 @@
           <t>C30</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F221" t="n">
         <v>3</v>
       </c>
@@ -5759,7 +6531,11 @@
           <t>C30</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F222" t="n">
         <v>2</v>
       </c>
@@ -5783,7 +6559,11 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F223" t="n">
         <v>1</v>
       </c>
@@ -5807,7 +6587,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
       <c r="F224" t="n">
         <v>14</v>
       </c>
@@ -5831,7 +6615,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F225" t="n">
         <v>20</v>
       </c>
@@ -5879,7 +6667,11 @@
           <t>C21</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
       <c r="F227" t="n">
         <v>1</v>
       </c>
@@ -5927,7 +6719,11 @@
           <t>C10</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
       <c r="F229" t="n">
         <v>1</v>
       </c>
@@ -5951,7 +6747,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
       <c r="F230" t="n">
         <v>2</v>
       </c>
@@ -5975,7 +6775,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>K63</t>
+        </is>
+      </c>
       <c r="F231" t="n">
         <v>5</v>
       </c>
@@ -5999,7 +6803,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F232" t="n">
         <v>2</v>
       </c>
@@ -6047,7 +6855,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
       <c r="F234" t="n">
         <v>2</v>
       </c>
@@ -6071,7 +6883,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F235" t="n">
         <v>1</v>
       </c>
@@ -6095,7 +6911,11 @@
           <t>N69</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F236" t="n">
         <v>3</v>
       </c>
@@ -6119,7 +6939,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F237" t="n">
         <v>1</v>
       </c>
@@ -6143,7 +6967,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
       <c r="F238" t="n">
         <v>2</v>
       </c>
@@ -6167,7 +6995,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F239" t="n">
         <v>8</v>
       </c>
@@ -6191,7 +7023,11 @@
           <t>C24</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F240" t="n">
         <v>2</v>
       </c>
@@ -6215,7 +7051,11 @@
           <t>A03</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
       <c r="F241" t="n">
         <v>1</v>
       </c>
@@ -6239,7 +7079,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
       <c r="F242" t="n">
         <v>2</v>
       </c>
@@ -6263,7 +7107,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F243" t="n">
         <v>5</v>
       </c>
@@ -6287,7 +7135,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F244" t="n">
         <v>2</v>
       </c>
@@ -6359,7 +7211,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
       <c r="F247" t="n">
         <v>2</v>
       </c>
@@ -6407,7 +7263,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F249" t="n">
         <v>1</v>
       </c>
@@ -6431,7 +7291,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F250" t="n">
         <v>1</v>
       </c>
@@ -6455,7 +7319,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F251" t="n">
         <v>1</v>
       </c>
@@ -6476,10 +7344,14 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>N70</t>
+        </is>
+      </c>
       <c r="F252" t="n">
         <v>1</v>
       </c>
@@ -6503,7 +7375,11 @@
           <t>R88</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F253" t="n">
         <v>1</v>
       </c>
@@ -6524,10 +7400,14 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F254" t="n">
         <v>1</v>
       </c>
@@ -6551,7 +7431,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F255" t="n">
         <v>1</v>
       </c>
@@ -6575,7 +7459,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F256" t="n">
         <v>1</v>
       </c>
@@ -6599,7 +7487,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F257" t="n">
         <v>1</v>
       </c>
@@ -6623,7 +7515,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
       <c r="F258" t="n">
         <v>1</v>
       </c>
@@ -6644,10 +7540,14 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F259" t="n">
         <v>1</v>
       </c>
@@ -6668,10 +7568,14 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F260" t="n">
         <v>1</v>
       </c>
@@ -6695,7 +7599,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F261" t="n">
         <v>1</v>
       </c>
@@ -6716,10 +7624,14 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F262" t="n">
         <v>1</v>
       </c>
@@ -6743,7 +7655,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>O80</t>
+        </is>
+      </c>
       <c r="F263" t="n">
         <v>1</v>
       </c>
@@ -6764,10 +7680,14 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F264" t="n">
         <v>1</v>
       </c>
@@ -6788,10 +7708,14 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F265" t="n">
         <v>1</v>
       </c>
@@ -6812,10 +7736,14 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr"/>
+          <t>R88</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F266" t="n">
         <v>1</v>
       </c>
@@ -6839,7 +7767,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>O80</t>
+        </is>
+      </c>
       <c r="F267" t="n">
         <v>1</v>
       </c>
@@ -6863,7 +7795,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F268" t="n">
         <v>1</v>
       </c>
@@ -6884,10 +7820,14 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F269" t="n">
         <v>1</v>
       </c>
@@ -6911,7 +7851,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F270" t="n">
         <v>1</v>
       </c>
@@ -6932,10 +7876,14 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>C21</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F271" t="n">
         <v>1</v>
       </c>
@@ -6956,10 +7904,14 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F272" t="n">
         <v>1</v>
       </c>
@@ -6983,7 +7935,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F273" t="n">
         <v>1</v>
       </c>
@@ -6994,7 +7950,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7031,7 +7987,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F275" t="n">
         <v>1</v>
       </c>
@@ -7052,10 +8012,14 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F276" t="n">
         <v>1</v>
       </c>
@@ -7076,10 +8040,14 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr"/>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F277" t="n">
         <v>1</v>
       </c>
@@ -7127,7 +8095,11 @@
           <t>O78</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F279" t="n">
         <v>1</v>
       </c>
@@ -7151,7 +8123,11 @@
           <t>A02</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F280" t="n">
         <v>1</v>
       </c>
@@ -7175,7 +8151,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F281" t="n">
         <v>1</v>
       </c>
@@ -7199,7 +8179,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F282" t="n">
         <v>1</v>
       </c>
@@ -7220,10 +8204,14 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr"/>
+          <t>I56</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F283" t="n">
         <v>1</v>
       </c>
@@ -7268,10 +8256,14 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F285" t="n">
         <v>1</v>
       </c>
@@ -7292,10 +8284,14 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr"/>
+          <t>R88</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F286" t="n">
         <v>1</v>
       </c>
@@ -7316,10 +8312,14 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F287" t="n">
         <v>1</v>
       </c>
@@ -7343,7 +8343,11 @@
           <t>C14</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F288" t="n">
         <v>1</v>
       </c>
@@ -7364,10 +8368,14 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F289" t="n">
         <v>1</v>
       </c>
@@ -7388,10 +8396,14 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F290" t="n">
         <v>1</v>
       </c>
@@ -7415,7 +8427,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F291" t="n">
         <v>1</v>
       </c>
@@ -7426,7 +8442,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7439,7 +8455,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F292" t="n">
         <v>1</v>
       </c>
@@ -7463,7 +8483,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F293" t="n">
         <v>1</v>
       </c>
@@ -7487,7 +8511,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F294" t="n">
         <v>1</v>
       </c>
@@ -7508,10 +8536,14 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
           <t>O78</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr"/>
       <c r="F295" t="n">
         <v>1</v>
       </c>
@@ -7535,7 +8567,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F296" t="n">
         <v>1</v>
       </c>
@@ -7546,7 +8582,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7556,10 +8592,14 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F297" t="n">
         <v>1</v>
       </c>
@@ -7580,10 +8620,14 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F298" t="n">
         <v>1</v>
       </c>
@@ -7604,10 +8648,14 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
           <t>R86</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
         <v>1</v>
       </c>
@@ -7618,7 +8666,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7628,10 +8676,14 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F300" t="n">
         <v>1</v>
       </c>
@@ -7652,10 +8704,14 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F301" t="n">
         <v>1</v>
       </c>
@@ -7703,7 +8759,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F303" t="n">
         <v>1</v>
       </c>
@@ -7727,7 +8787,11 @@
           <t>B07</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F304" t="n">
         <v>1</v>
       </c>
@@ -7751,7 +8815,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F305" t="n">
         <v>1</v>
       </c>
@@ -7762,7 +8830,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7772,10 +8840,14 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F306" t="n">
         <v>1</v>
       </c>
@@ -7799,7 +8871,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F307" t="n">
         <v>1</v>
       </c>
@@ -7823,7 +8899,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F308" t="n">
         <v>1</v>
       </c>
@@ -7847,7 +8927,11 @@
           <t>R88</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F309" t="n">
         <v>1</v>
       </c>
@@ -7858,7 +8942,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7871,7 +8955,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F310" t="n">
         <v>1</v>
       </c>
@@ -7892,10 +8980,14 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F311" t="n">
         <v>1</v>
       </c>
@@ -7916,10 +9008,14 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F312" t="n">
         <v>1</v>
       </c>
@@ -7943,7 +9039,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F313" t="n">
         <v>1</v>
       </c>
@@ -7964,10 +9064,14 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
+          <t>R88</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
           <t>L64</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr"/>
       <c r="F314" t="n">
         <v>1</v>
       </c>
@@ -7991,7 +9095,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F315" t="n">
         <v>1</v>
       </c>
@@ -8012,10 +9120,14 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr"/>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F316" t="n">
         <v>1</v>
       </c>
@@ -8039,7 +9151,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F317" t="n">
         <v>1</v>
       </c>
@@ -8060,10 +9176,14 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F318" t="n">
         <v>1</v>
       </c>
@@ -8074,7 +9194,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -8087,7 +9207,11 @@
           <t>C26</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F319" t="n">
         <v>1</v>
       </c>
@@ -8111,7 +9235,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F320" t="n">
         <v>1</v>
       </c>
@@ -8135,7 +9263,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F321" t="n">
         <v>1</v>
       </c>
@@ -8156,10 +9288,14 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F322" t="n">
         <v>1</v>
       </c>
@@ -8180,10 +9316,14 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr"/>
+          <t>R86</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F323" t="n">
         <v>1</v>
       </c>
@@ -8204,10 +9344,14 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
       <c r="F324" t="n">
         <v>1</v>
       </c>
@@ -8231,7 +9375,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F325" t="n">
         <v>1</v>
       </c>
@@ -8252,10 +9400,14 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr"/>
       <c r="F326" t="n">
         <v>1</v>
       </c>
@@ -8276,10 +9428,14 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F327" t="n">
         <v>1</v>
       </c>
@@ -8300,10 +9456,14 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
           <t>J60</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>1</v>
       </c>
@@ -8324,10 +9484,14 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F329" t="n">
         <v>1</v>
       </c>
@@ -8348,10 +9512,14 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F330" t="n">
         <v>1</v>
       </c>
@@ -8375,7 +9543,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F331" t="n">
         <v>1</v>
       </c>
@@ -8386,7 +9558,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -8396,10 +9568,14 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F332" t="n">
         <v>1</v>
       </c>
@@ -8420,10 +9596,14 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F333" t="n">
         <v>1</v>
       </c>
@@ -8444,10 +9624,14 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
           <t>S90</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>1</v>
       </c>
@@ -8471,7 +9655,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F335" t="n">
         <v>1</v>
       </c>
@@ -8495,7 +9683,11 @@
           <t>E38</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F336" t="n">
         <v>1</v>
       </c>
@@ -8516,10 +9708,14 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
           <t>P84</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>1</v>
       </c>
@@ -8543,7 +9739,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F338" t="n">
         <v>1</v>
       </c>
@@ -8564,10 +9764,14 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F339" t="n">
         <v>1</v>
       </c>
@@ -8588,10 +9792,14 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F340" t="n">
         <v>1</v>
       </c>
@@ -8612,10 +9820,14 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F341" t="n">
         <v>1</v>
       </c>
@@ -8636,10 +9848,14 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
       <c r="F342" t="n">
         <v>1</v>
       </c>
@@ -8660,10 +9876,14 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F343" t="n">
         <v>1</v>
       </c>
@@ -8684,10 +9904,14 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F344" t="n">
         <v>1</v>
       </c>
@@ -8698,7 +9922,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8708,10 +9932,14 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F345" t="n">
         <v>1</v>
       </c>
@@ -8732,10 +9960,14 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>R88</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F346" t="n">
         <v>1</v>
       </c>
@@ -8756,10 +9988,14 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
           <t>S90</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr"/>
       <c r="F347" t="n">
         <v>1</v>
       </c>
@@ -8807,7 +10043,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F349" t="n">
         <v>1</v>
       </c>
@@ -8831,7 +10071,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F350" t="n">
         <v>1</v>
       </c>
@@ -8852,10 +10096,14 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr"/>
+          <t>F41</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F351" t="n">
         <v>1</v>
       </c>
@@ -8879,7 +10127,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F352" t="n">
         <v>1</v>
       </c>
@@ -8900,10 +10152,14 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F353" t="n">
         <v>1</v>
       </c>
@@ -8924,10 +10180,14 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F354" t="n">
         <v>1</v>
       </c>
@@ -8951,7 +10211,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F355" t="n">
         <v>1</v>
       </c>
@@ -8975,7 +10239,11 @@
           <t>C10</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>H52</t>
+        </is>
+      </c>
       <c r="F356" t="n">
         <v>1</v>
       </c>
@@ -8996,10 +10264,14 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F357" t="n">
         <v>1</v>
       </c>
@@ -9023,7 +10295,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
       <c r="F358" t="n">
         <v>1</v>
       </c>
@@ -9071,7 +10347,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F360" t="n">
         <v>1</v>
       </c>
@@ -9092,10 +10372,14 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr"/>
       <c r="F361" t="n">
         <v>1</v>
       </c>
@@ -9116,10 +10400,14 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F362" t="n">
         <v>1</v>
       </c>
@@ -9143,7 +10431,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F363" t="n">
         <v>1</v>
       </c>
@@ -9154,7 +10446,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -9164,10 +10456,14 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
         <v>1</v>
       </c>
@@ -9191,7 +10487,11 @@
           <t>C27</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F365" t="n">
         <v>1</v>
       </c>
@@ -9215,7 +10515,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F366" t="n">
         <v>1</v>
       </c>
@@ -9260,10 +10564,14 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr"/>
+          <t>N70</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F368" t="n">
         <v>1</v>
       </c>
@@ -9287,7 +10595,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
       <c r="F369" t="n">
         <v>1</v>
       </c>
@@ -9298,7 +10610,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -9308,10 +10620,14 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F370" t="n">
         <v>1</v>
       </c>
@@ -9335,7 +10651,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F371" t="n">
         <v>1</v>
       </c>
@@ -9380,10 +10700,14 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F373" t="n">
         <v>1</v>
       </c>
@@ -9407,7 +10731,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F374" t="n">
         <v>1</v>
       </c>
@@ -9428,10 +10756,14 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F375" t="n">
         <v>1</v>
       </c>
@@ -9452,10 +10784,14 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F376" t="n">
         <v>1</v>
       </c>
@@ -9479,7 +10815,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F377" t="n">
         <v>1</v>
       </c>
@@ -9500,10 +10840,14 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr"/>
+          <t>J58</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F378" t="n">
         <v>1</v>
       </c>
@@ -9527,7 +10871,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F379" t="n">
         <v>1</v>
       </c>
@@ -9551,7 +10899,11 @@
           <t>J58</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F380" t="n">
         <v>1</v>
       </c>
@@ -9572,10 +10924,14 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr"/>
+          <t>R86</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
       <c r="F381" t="n">
         <v>1</v>
       </c>
@@ -9596,10 +10952,14 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>C27</t>
+        </is>
+      </c>
       <c r="F382" t="n">
         <v>1</v>
       </c>
@@ -9623,7 +10983,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F383" t="n">
         <v>1</v>
       </c>
@@ -9644,10 +11008,14 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F384" t="n">
         <v>1</v>
       </c>
@@ -9671,7 +11039,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F385" t="n">
         <v>1</v>
       </c>
@@ -9695,7 +11067,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F386" t="n">
         <v>1</v>
       </c>
@@ -9716,10 +11092,14 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr"/>
+          <t>H53</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F387" t="n">
         <v>1</v>
       </c>
@@ -9743,7 +11123,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
       <c r="F388" t="n">
         <v>1</v>
       </c>
@@ -9767,7 +11151,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F389" t="n">
         <v>1</v>
       </c>
@@ -9788,10 +11176,14 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F390" t="n">
         <v>1</v>
       </c>
@@ -9812,10 +11204,14 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F391" t="n">
         <v>1</v>
       </c>
@@ -9839,7 +11235,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
       <c r="F392" t="n">
         <v>1</v>
       </c>
@@ -9860,10 +11260,14 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F393" t="n">
         <v>1</v>
       </c>
@@ -9884,10 +11288,14 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F394" t="n">
         <v>1</v>
       </c>
@@ -9908,10 +11316,14 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F395" t="n">
         <v>1</v>
       </c>
@@ -9935,7 +11347,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
       <c r="F396" t="n">
         <v>1</v>
       </c>
@@ -9959,7 +11375,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F397" t="n">
         <v>1</v>
       </c>
@@ -9980,10 +11400,14 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F398" t="n">
         <v>1</v>
       </c>
@@ -10004,10 +11428,14 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F399" t="n">
         <v>1</v>
       </c>
@@ -10031,7 +11459,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F400" t="n">
         <v>1</v>
       </c>
@@ -10076,10 +11508,14 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F402" t="n">
         <v>1</v>
       </c>
@@ -10100,10 +11536,14 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F403" t="n">
         <v>1</v>
       </c>
@@ -10114,7 +11554,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -10124,10 +11564,14 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
         <v>1</v>
       </c>
@@ -10151,7 +11595,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F405" t="n">
         <v>1</v>
       </c>
@@ -10196,10 +11644,14 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F407" t="n">
         <v>1</v>
       </c>
@@ -10220,10 +11672,14 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F408" t="n">
         <v>1</v>
       </c>
@@ -10244,10 +11700,14 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
+          <t>J58</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F409" t="n">
         <v>1</v>
       </c>
@@ -10271,7 +11731,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F410" t="n">
         <v>1</v>
       </c>
@@ -10316,10 +11780,14 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F412" t="n">
         <v>1</v>
       </c>
@@ -10343,7 +11811,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F413" t="n">
         <v>1</v>
       </c>
@@ -10364,10 +11836,14 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F414" t="n">
         <v>1</v>
       </c>
@@ -10391,7 +11867,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F415" t="n">
         <v>1</v>
       </c>
@@ -10415,7 +11895,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F416" t="n">
         <v>1</v>
       </c>
@@ -10426,7 +11910,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -10436,10 +11920,14 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F417" t="n">
         <v>1</v>
       </c>
@@ -10460,10 +11948,14 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F418" t="n">
         <v>1</v>
       </c>
@@ -10487,7 +11979,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr"/>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>O80</t>
+        </is>
+      </c>
       <c r="F419" t="n">
         <v>1</v>
       </c>
@@ -10511,7 +12007,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F420" t="n">
         <v>1</v>
       </c>
@@ -10532,10 +12032,14 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>J60</t>
+        </is>
+      </c>
       <c r="F421" t="n">
         <v>1</v>
       </c>
@@ -10556,10 +12060,14 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F422" t="n">
         <v>1</v>
       </c>
@@ -10607,7 +12115,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E424" t="inlineStr"/>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>N69</t>
+        </is>
+      </c>
       <c r="F424" t="n">
         <v>1</v>
       </c>
@@ -10631,7 +12143,11 @@
           <t>H51</t>
         </is>
       </c>
-      <c r="E425" t="inlineStr"/>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F425" t="n">
         <v>1</v>
       </c>
@@ -10655,7 +12171,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr"/>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F426" t="n">
         <v>1</v>
       </c>
@@ -10679,7 +12199,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E427" t="inlineStr"/>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F427" t="n">
         <v>1</v>
       </c>
@@ -10703,7 +12227,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr"/>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F428" t="n">
         <v>1</v>
       </c>
@@ -10727,7 +12255,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F429" t="n">
         <v>1</v>
       </c>
@@ -10748,10 +12280,14 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F430" t="n">
         <v>1</v>
       </c>
@@ -10772,10 +12308,14 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F431" t="n">
         <v>1</v>
       </c>
@@ -10796,10 +12336,14 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F432" t="n">
         <v>1</v>
       </c>
@@ -10820,10 +12364,14 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr"/>
+          <t>O79</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F433" t="n">
         <v>1</v>
       </c>
@@ -10847,7 +12395,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
       <c r="F434" t="n">
         <v>1</v>
       </c>
@@ -10868,10 +12420,14 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F435" t="n">
         <v>1</v>
       </c>
@@ -10892,10 +12448,14 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>J59</t>
+        </is>
+      </c>
       <c r="F436" t="n">
         <v>1</v>
       </c>
@@ -10916,10 +12476,14 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F437" t="n">
         <v>1</v>
       </c>
@@ -10940,10 +12504,14 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>R86</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F438" t="n">
         <v>1</v>
       </c>
@@ -10964,10 +12532,14 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F439" t="n">
         <v>1</v>
       </c>
@@ -10988,10 +12560,14 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>J58</t>
+        </is>
+      </c>
       <c r="F440" t="n">
         <v>1</v>
       </c>
@@ -11012,10 +12588,14 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F441" t="n">
         <v>1</v>
       </c>
@@ -11063,7 +12643,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E443" t="inlineStr"/>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F443" t="n">
         <v>1</v>
       </c>
@@ -11087,7 +12671,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E444" t="inlineStr"/>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F444" t="n">
         <v>1</v>
       </c>
@@ -11098,7 +12686,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -11111,7 +12699,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>F41</t>
+        </is>
+      </c>
       <c r="F445" t="n">
         <v>1</v>
       </c>
@@ -11135,7 +12727,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr"/>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F446" t="n">
         <v>1</v>
       </c>
@@ -11159,7 +12755,11 @@
           <t>J60</t>
         </is>
       </c>
-      <c r="E447" t="inlineStr"/>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F447" t="n">
         <v>1</v>
       </c>
@@ -11180,10 +12780,14 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr"/>
+          <t>J58</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F448" t="n">
         <v>1</v>
       </c>
@@ -11204,10 +12808,14 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F449" t="n">
         <v>1</v>
       </c>
@@ -11231,7 +12839,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E450" t="inlineStr"/>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F450" t="n">
         <v>1</v>
       </c>
@@ -11279,7 +12891,11 @@
           <t>R88</t>
         </is>
       </c>
-      <c r="E452" t="inlineStr"/>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F452" t="n">
         <v>1</v>
       </c>
@@ -11300,10 +12916,14 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F453" t="n">
         <v>1</v>
       </c>
@@ -11327,7 +12947,11 @@
           <t>R88</t>
         </is>
       </c>
-      <c r="E454" t="inlineStr"/>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F454" t="n">
         <v>1</v>
       </c>
@@ -11338,7 +12962,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -11348,10 +12972,14 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F455" t="n">
         <v>1</v>
       </c>
@@ -11375,7 +13003,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E456" t="inlineStr"/>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>F41</t>
+        </is>
+      </c>
       <c r="F456" t="n">
         <v>1</v>
       </c>
@@ -11396,10 +13028,14 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F457" t="n">
         <v>1</v>
       </c>
@@ -11423,7 +13059,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E458" t="inlineStr"/>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F458" t="n">
         <v>1</v>
       </c>
@@ -11444,10 +13084,14 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F459" t="n">
         <v>1</v>
       </c>
@@ -11468,10 +13112,14 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F460" t="n">
         <v>1</v>
       </c>
@@ -11492,10 +13140,14 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F461" t="n">
         <v>1</v>
       </c>
@@ -11543,7 +13195,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E463" t="inlineStr"/>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F463" t="n">
         <v>1</v>
       </c>
@@ -11564,10 +13220,14 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
           <t>L64</t>
         </is>
       </c>
-      <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
         <v>1</v>
       </c>
@@ -11591,7 +13251,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E465" t="inlineStr"/>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F465" t="n">
         <v>1</v>
       </c>
@@ -11602,7 +13266,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -11612,10 +13276,14 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E466" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
       <c r="F466" t="n">
         <v>1</v>
       </c>
@@ -11636,10 +13304,14 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E467" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F467" t="n">
         <v>1</v>
       </c>
@@ -11663,7 +13335,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E468" t="inlineStr"/>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F468" t="n">
         <v>1</v>
       </c>
@@ -11684,10 +13360,14 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E469" t="inlineStr"/>
+          <t>O79</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F469" t="n">
         <v>1</v>
       </c>
@@ -11732,10 +13412,14 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F471" t="n">
         <v>1</v>
       </c>
@@ -11831,7 +13515,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E475" t="inlineStr"/>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F475" t="n">
         <v>1</v>
       </c>
@@ -11855,7 +13543,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr"/>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F476" t="n">
         <v>1</v>
       </c>
@@ -11876,10 +13568,14 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F477" t="n">
         <v>1</v>
       </c>
@@ -11900,10 +13596,14 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
       <c r="F478" t="n">
         <v>1</v>
       </c>
@@ -11924,10 +13624,14 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F479" t="n">
         <v>1</v>
       </c>
@@ -11951,7 +13655,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E480" t="inlineStr"/>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F480" t="n">
         <v>1</v>
       </c>
@@ -11975,7 +13683,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E481" t="inlineStr"/>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F481" t="n">
         <v>1</v>
       </c>
@@ -11999,7 +13711,11 @@
           <t>C26</t>
         </is>
       </c>
-      <c r="E482" t="inlineStr"/>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F482" t="n">
         <v>1</v>
       </c>
@@ -12020,10 +13736,14 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="E483" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F483" t="n">
         <v>1</v>
       </c>
@@ -12047,7 +13767,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E484" t="inlineStr"/>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F484" t="n">
         <v>1</v>
       </c>
@@ -12068,10 +13792,14 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr"/>
+          <t>R86</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F485" t="n">
         <v>1</v>
       </c>
@@ -12095,7 +13823,11 @@
           <t>C14</t>
         </is>
       </c>
-      <c r="E486" t="inlineStr"/>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F486" t="n">
         <v>1</v>
       </c>
@@ -12119,7 +13851,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E487" t="inlineStr"/>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F487" t="n">
         <v>1</v>
       </c>
@@ -12140,10 +13876,14 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr"/>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F488" t="n">
         <v>1</v>
       </c>
@@ -12164,10 +13904,14 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
         <v>1</v>
       </c>
@@ -12188,10 +13932,14 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F490" t="n">
         <v>1</v>
       </c>
@@ -12215,7 +13963,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E491" t="inlineStr"/>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F491" t="n">
         <v>1</v>
       </c>
@@ -12236,10 +13988,14 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
           <t>B06</t>
         </is>
       </c>
-      <c r="E492" t="inlineStr"/>
       <c r="F492" t="n">
         <v>1</v>
       </c>
@@ -12263,7 +14019,11 @@
           <t>C29</t>
         </is>
       </c>
-      <c r="E493" t="inlineStr"/>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>J58</t>
+        </is>
+      </c>
       <c r="F493" t="n">
         <v>1</v>
       </c>
@@ -12287,7 +14047,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr"/>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F494" t="n">
         <v>1</v>
       </c>
@@ -12311,7 +14075,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E495" t="inlineStr"/>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F495" t="n">
         <v>1</v>
       </c>
@@ -12332,10 +14100,14 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F496" t="n">
         <v>1</v>
       </c>
@@ -12356,10 +14128,14 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
           <t>S90</t>
         </is>
       </c>
-      <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
         <v>1</v>
       </c>
@@ -12383,7 +14159,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E498" t="inlineStr"/>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F498" t="n">
         <v>1</v>
       </c>
@@ -12404,10 +14184,14 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr"/>
+          <t>S90</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F499" t="n">
         <v>1</v>
       </c>
@@ -12452,10 +14236,14 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E501" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F501" t="n">
         <v>1</v>
       </c>
@@ -12476,10 +14264,14 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E502" t="inlineStr"/>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F502" t="n">
         <v>1</v>
       </c>
@@ -12503,7 +14295,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr"/>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F503" t="n">
         <v>1</v>
       </c>
@@ -12527,7 +14323,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F504" t="n">
         <v>1</v>
       </c>
@@ -12551,7 +14351,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E505" t="inlineStr"/>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F505" t="n">
         <v>1</v>
       </c>
@@ -12575,7 +14379,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E506" t="inlineStr"/>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F506" t="n">
         <v>1</v>
       </c>
@@ -12596,10 +14404,14 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E507" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F507" t="n">
         <v>1</v>
       </c>
@@ -12620,10 +14432,14 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E508" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>O78</t>
+        </is>
+      </c>
       <c r="F508" t="n">
         <v>1</v>
       </c>
@@ -12647,7 +14463,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E509" t="inlineStr"/>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F509" t="n">
         <v>1</v>
       </c>
@@ -12671,7 +14491,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr"/>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F510" t="n">
         <v>1</v>
       </c>
@@ -12695,7 +14519,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr"/>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
       <c r="F511" t="n">
         <v>1</v>
       </c>
@@ -12719,7 +14547,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr"/>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F512" t="n">
         <v>1</v>
       </c>
@@ -12730,7 +14562,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -12740,10 +14572,14 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr"/>
       <c r="F513" t="n">
         <v>1</v>
       </c>
@@ -12764,10 +14600,14 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
           <t>R88</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr"/>
       <c r="F514" t="n">
         <v>1</v>
       </c>
@@ -12788,10 +14628,14 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>J58</t>
-        </is>
-      </c>
-      <c r="E515" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F515" t="n">
         <v>1</v>
       </c>
@@ -12812,10 +14656,14 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E516" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F516" t="n">
         <v>1</v>
       </c>
@@ -12839,7 +14687,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E517" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F517" t="n">
         <v>1</v>
       </c>
@@ -12863,7 +14715,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E518" t="inlineStr"/>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F518" t="n">
         <v>1</v>
       </c>
@@ -12887,7 +14743,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E519" t="inlineStr"/>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F519" t="n">
         <v>1</v>
       </c>
@@ -12908,10 +14768,14 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E520" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F520" t="n">
         <v>1</v>
       </c>
@@ -12922,7 +14786,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -12932,10 +14796,14 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E521" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F521" t="n">
         <v>1</v>
       </c>
@@ -12959,7 +14827,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr"/>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
       <c r="F522" t="n">
         <v>1</v>
       </c>
@@ -12980,10 +14852,14 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E523" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F523" t="n">
         <v>1</v>
       </c>
@@ -13004,10 +14880,14 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E524" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F524" t="n">
         <v>1</v>
       </c>
@@ -13028,10 +14908,14 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>N69</t>
-        </is>
-      </c>
-      <c r="E525" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F525" t="n">
         <v>1</v>
       </c>
@@ -13052,10 +14936,14 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F526" t="n">
         <v>1</v>
       </c>
@@ -13076,10 +14964,14 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E527" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F527" t="n">
         <v>1</v>
       </c>
@@ -13103,7 +14995,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E528" t="inlineStr"/>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F528" t="n">
         <v>1</v>
       </c>
@@ -13124,10 +15020,14 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E529" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F529" t="n">
         <v>1</v>
       </c>
@@ -13151,7 +15051,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr"/>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
       <c r="F530" t="n">
         <v>1</v>
       </c>
@@ -13199,7 +15103,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E532" t="inlineStr"/>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F532" t="n">
         <v>1</v>
       </c>
@@ -13223,7 +15131,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E533" t="inlineStr"/>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F533" t="n">
         <v>1</v>
       </c>
@@ -13244,10 +15156,14 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E534" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F534" t="n">
         <v>1</v>
       </c>
@@ -13271,7 +15187,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>R86</t>
+        </is>
+      </c>
       <c r="F535" t="n">
         <v>1</v>
       </c>
@@ -13295,7 +15215,11 @@
           <t>R88</t>
         </is>
       </c>
-      <c r="E536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F536" t="n">
         <v>1</v>
       </c>
@@ -13316,10 +15240,14 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>E38</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F537" t="n">
         <v>1</v>
       </c>
@@ -13354,7 +15282,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -13364,10 +15292,14 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F539" t="n">
         <v>1</v>
       </c>
@@ -13391,7 +15323,11 @@
           <t>B06</t>
         </is>
       </c>
-      <c r="E540" t="inlineStr"/>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
       <c r="F540" t="n">
         <v>1</v>
       </c>
@@ -13415,7 +15351,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E541" t="inlineStr"/>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F541" t="n">
         <v>1</v>
       </c>
@@ -13439,7 +15379,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E542" t="inlineStr"/>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F542" t="n">
         <v>1</v>
       </c>
@@ -13460,10 +15404,14 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F543" t="n">
         <v>1</v>
       </c>
@@ -13487,7 +15435,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E544" t="inlineStr"/>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F544" t="n">
         <v>1</v>
       </c>
@@ -13532,10 +15484,14 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E546" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F546" t="n">
         <v>1</v>
       </c>
@@ -13556,10 +15512,14 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E547" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F547" t="n">
         <v>1</v>
       </c>
@@ -13607,7 +15567,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E549" t="inlineStr"/>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F549" t="n">
         <v>1</v>
       </c>
@@ -13628,10 +15592,14 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E550" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F550" t="n">
         <v>1</v>
       </c>
@@ -13652,10 +15620,14 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E551" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F551" t="n">
         <v>1</v>
       </c>
@@ -13679,7 +15651,11 @@
           <t>R88</t>
         </is>
       </c>
-      <c r="E552" t="inlineStr"/>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F552" t="n">
         <v>1</v>
       </c>
@@ -13724,10 +15700,14 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F554" t="n">
         <v>1</v>
       </c>
@@ -13738,7 +15718,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -13748,10 +15728,14 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F555" t="n">
         <v>1</v>
       </c>
@@ -13772,10 +15756,14 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E556" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F556" t="n">
         <v>1</v>
       </c>
@@ -13820,10 +15808,14 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr"/>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F558" t="n">
         <v>1</v>
       </c>
@@ -13834,7 +15826,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -13844,10 +15836,14 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>O78</t>
+        </is>
+      </c>
       <c r="F559" t="n">
         <v>1</v>
       </c>
@@ -13871,7 +15867,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E560" t="inlineStr"/>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F560" t="n">
         <v>1</v>
       </c>
@@ -13906,7 +15906,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -13916,10 +15916,14 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E562" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
       <c r="F562" t="n">
         <v>1</v>
       </c>
@@ -13943,7 +15947,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E563" t="inlineStr"/>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F563" t="n">
         <v>1</v>
       </c>
@@ -13964,10 +15972,14 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E564" t="inlineStr"/>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F564" t="n">
         <v>1</v>
       </c>
@@ -13991,7 +16003,11 @@
           <t>O79</t>
         </is>
       </c>
-      <c r="E565" t="inlineStr"/>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F565" t="n">
         <v>1</v>
       </c>
@@ -14015,7 +16031,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E566" t="inlineStr"/>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F566" t="n">
         <v>1</v>
       </c>
@@ -14036,10 +16056,14 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>O80</t>
+        </is>
+      </c>
       <c r="F567" t="n">
         <v>1</v>
       </c>
@@ -14084,10 +16108,14 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F569" t="n">
         <v>1</v>
       </c>
@@ -14098,7 +16126,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -14111,7 +16139,11 @@
           <t>C17</t>
         </is>
       </c>
-      <c r="E570" t="inlineStr"/>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F570" t="n">
         <v>1</v>
       </c>
@@ -14122,7 +16154,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -14132,10 +16164,14 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F571" t="n">
         <v>1</v>
       </c>
@@ -14156,10 +16192,14 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E572" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>O80</t>
+        </is>
+      </c>
       <c r="F572" t="n">
         <v>1</v>
       </c>
@@ -14180,10 +16220,14 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E573" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>I55</t>
+        </is>
+      </c>
       <c r="F573" t="n">
         <v>1</v>
       </c>
@@ -14194,7 +16238,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -14204,10 +16248,14 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E574" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F574" t="n">
         <v>1</v>
       </c>
@@ -14252,10 +16300,14 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="E576" t="inlineStr"/>
       <c r="F576" t="n">
         <v>1</v>
       </c>
@@ -14276,10 +16328,14 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E577" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F577" t="n">
         <v>1</v>
       </c>
@@ -14290,7 +16346,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -14300,10 +16356,14 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>1</v>
       </c>
@@ -14327,7 +16387,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>1</v>
       </c>
@@ -14351,7 +16415,11 @@
           <t>R86</t>
         </is>
       </c>
-      <c r="E580" t="inlineStr"/>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F580" t="n">
         <v>1</v>
       </c>
@@ -14375,7 +16443,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E581" t="inlineStr"/>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F581" t="n">
         <v>1</v>
       </c>
@@ -14396,10 +16468,14 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E582" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F582" t="n">
         <v>1</v>
       </c>
@@ -14444,10 +16520,14 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E584" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F584" t="n">
         <v>1</v>
       </c>
@@ -14468,10 +16548,14 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E585" t="inlineStr"/>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>J58</t>
+        </is>
+      </c>
       <c r="F585" t="n">
         <v>1</v>
       </c>
@@ -14482,7 +16566,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -14492,10 +16576,14 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="E586" t="inlineStr"/>
+          <t>R86</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F586" t="n">
         <v>1</v>
       </c>
@@ -14516,10 +16604,14 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E587" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F587" t="n">
         <v>1</v>
       </c>
@@ -14540,10 +16632,14 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E588" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F588" t="n">
         <v>1</v>
       </c>
@@ -14564,10 +16660,14 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F589" t="n">
         <v>1</v>
       </c>
@@ -14591,7 +16691,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E590" t="inlineStr"/>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F590" t="n">
         <v>1</v>
       </c>
@@ -14615,7 +16719,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E591" t="inlineStr"/>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>O79</t>
+        </is>
+      </c>
       <c r="F591" t="n">
         <v>1</v>
       </c>
@@ -14639,7 +16747,11 @@
           <t>A01</t>
         </is>
       </c>
-      <c r="E592" t="inlineStr"/>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F592" t="n">
         <v>1</v>
       </c>
@@ -14660,10 +16772,14 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F593" t="n">
         <v>1</v>
       </c>
@@ -14687,7 +16803,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E594" t="inlineStr"/>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F594" t="n">
         <v>1</v>
       </c>
@@ -14708,10 +16828,14 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
           <t>Q85</t>
         </is>
       </c>
-      <c r="E595" t="inlineStr"/>
       <c r="F595" t="n">
         <v>1</v>
       </c>
@@ -14735,7 +16859,11 @@
           <t>K62</t>
         </is>
       </c>
-      <c r="E596" t="inlineStr"/>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F596" t="n">
         <v>1</v>
       </c>
@@ -14756,10 +16884,14 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F597" t="n">
         <v>1</v>
       </c>
@@ -14804,10 +16936,14 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr"/>
+          <t>F41</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F599" t="n">
         <v>1</v>
       </c>
@@ -14831,7 +16967,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E600" t="inlineStr"/>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F600" t="n">
         <v>1</v>
       </c>
@@ -14855,7 +16995,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E601" t="inlineStr"/>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F601" t="n">
         <v>1</v>
       </c>
@@ -14879,7 +17023,11 @@
           <t>E36</t>
         </is>
       </c>
-      <c r="E602" t="inlineStr"/>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F602" t="n">
         <v>1</v>
       </c>
@@ -14924,10 +17072,14 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E604" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F604" t="n">
         <v>1</v>
       </c>
@@ -14951,7 +17103,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E605" t="inlineStr"/>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>J58</t>
+        </is>
+      </c>
       <c r="F605" t="n">
         <v>1</v>
       </c>
@@ -14972,10 +17128,14 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E606" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F606" t="n">
         <v>1</v>
       </c>
@@ -14996,10 +17156,14 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E607" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F607" t="n">
         <v>1</v>
       </c>
@@ -15023,7 +17187,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E608" t="inlineStr"/>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
       <c r="F608" t="n">
         <v>1</v>
       </c>
@@ -15044,10 +17212,14 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E609" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F609" t="n">
         <v>1</v>
       </c>
@@ -15071,7 +17243,11 @@
           <t>C23</t>
         </is>
       </c>
-      <c r="E610" t="inlineStr"/>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F610" t="n">
         <v>1</v>
       </c>
@@ -15095,7 +17271,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E611" t="inlineStr"/>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F611" t="n">
         <v>1</v>
       </c>
@@ -15143,7 +17323,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E613" t="inlineStr"/>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F613" t="n">
         <v>1</v>
       </c>
@@ -15154,7 +17338,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -15164,10 +17348,14 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E614" t="inlineStr"/>
+          <t>J58</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F614" t="n">
         <v>1</v>
       </c>
@@ -15191,7 +17379,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E615" t="inlineStr"/>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F615" t="n">
         <v>1</v>
       </c>
@@ -15212,10 +17404,14 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>N72</t>
-        </is>
-      </c>
-      <c r="E616" t="inlineStr"/>
+          <t>R86</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F616" t="n">
         <v>1</v>
       </c>
@@ -15239,7 +17435,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E617" t="inlineStr"/>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F617" t="n">
         <v>1</v>
       </c>
@@ -15250,7 +17450,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>OTHER_PROJECT</t>
+          <t>QD_PROJECT</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -15260,10 +17460,14 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E618" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F618" t="n">
         <v>1</v>
       </c>
@@ -15284,10 +17488,14 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E619" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F619" t="n">
         <v>1</v>
       </c>
@@ -15335,7 +17543,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E621" t="inlineStr"/>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F621" t="n">
         <v>1</v>
       </c>
@@ -15356,10 +17568,14 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E622" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F622" t="n">
         <v>1</v>
       </c>
@@ -15383,7 +17599,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E623" t="inlineStr"/>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
       <c r="F623" t="n">
         <v>1</v>
       </c>
@@ -15404,10 +17624,14 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>C30</t>
-        </is>
-      </c>
-      <c r="E624" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F624" t="n">
         <v>1</v>
       </c>
@@ -15428,10 +17652,14 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E625" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F625" t="n">
         <v>1</v>
       </c>
@@ -15455,7 +17683,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E626" t="inlineStr"/>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>L65</t>
+        </is>
+      </c>
       <c r="F626" t="n">
         <v>1</v>
       </c>
@@ -15500,10 +17732,14 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="E628" t="inlineStr"/>
+          <t>Q85</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>K62</t>
+        </is>
+      </c>
       <c r="F628" t="n">
         <v>1</v>
       </c>
@@ -15524,10 +17760,14 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="E629" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F629" t="n">
         <v>1</v>
       </c>
@@ -15551,7 +17791,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E630" t="inlineStr"/>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F630" t="n">
         <v>1</v>
       </c>
@@ -15572,10 +17816,14 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
           <t>O78</t>
         </is>
       </c>
-      <c r="E631" t="inlineStr"/>
       <c r="F631" t="n">
         <v>1</v>
       </c>
@@ -15599,7 +17847,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E632" t="inlineStr"/>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F632" t="n">
         <v>1</v>
       </c>
@@ -15671,7 +17923,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E635" t="inlineStr"/>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
       <c r="F635" t="n">
         <v>1</v>
       </c>
@@ -15692,10 +17948,14 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="E636" t="inlineStr"/>
+          <t>J58</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F636" t="n">
         <v>1</v>
       </c>
@@ -15719,7 +17979,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E637" t="inlineStr"/>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
       <c r="F637" t="n">
         <v>1</v>
       </c>
@@ -15743,7 +18007,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E638" t="inlineStr"/>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>N74</t>
+        </is>
+      </c>
       <c r="F638" t="n">
         <v>1</v>
       </c>
@@ -15764,10 +18032,14 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="E639" t="inlineStr"/>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>G47</t>
+        </is>
+      </c>
       <c r="F639" t="n">
         <v>1</v>
       </c>
@@ -15788,10 +18060,14 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>C21</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>R88</t>
+        </is>
+      </c>
       <c r="F640" t="n">
         <v>1</v>
       </c>
@@ -15815,7 +18091,11 @@
           <t>N72</t>
         </is>
       </c>
-      <c r="E641" t="inlineStr"/>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F641" t="n">
         <v>1</v>
       </c>
@@ -15836,10 +18116,14 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E642" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F642" t="n">
         <v>1</v>
       </c>
@@ -15863,7 +18147,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E643" t="inlineStr"/>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F643" t="n">
         <v>1</v>
       </c>
@@ -15884,10 +18172,14 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="E644" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
       <c r="F644" t="n">
         <v>1</v>
       </c>
@@ -15911,7 +18203,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E645" t="inlineStr"/>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F645" t="n">
         <v>1</v>
       </c>
@@ -15935,7 +18231,11 @@
           <t>Q85</t>
         </is>
       </c>
-      <c r="E646" t="inlineStr"/>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>N72</t>
+        </is>
+      </c>
       <c r="F646" t="n">
         <v>1</v>
       </c>
@@ -15956,10 +18256,14 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>K62</t>
-        </is>
-      </c>
-      <c r="E647" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
       <c r="F647" t="n">
         <v>1</v>
       </c>
@@ -15980,10 +18284,14 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="E648" t="inlineStr"/>
       <c r="F648" t="n">
         <v>1</v>
       </c>
@@ -16007,7 +18315,11 @@
           <t>S91</t>
         </is>
       </c>
-      <c r="E649" t="inlineStr"/>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
       <c r="F649" t="n">
         <v>1</v>
       </c>
@@ -16028,10 +18340,14 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>C29</t>
-        </is>
-      </c>
-      <c r="E650" t="inlineStr"/>
+          <t>N72</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Q85</t>
+        </is>
+      </c>
       <c r="F650" t="n">
         <v>1</v>
       </c>
